--- a/www/download/COUNTRY.LTU.EXI382.xlsx
+++ b/www/download/COUNTRY.LTU.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>Lituânia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20587239263804</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20587239263804</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20587239263804</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20587239263804</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20587239263804</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20587239263804</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20587239263804</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20587239263804</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20587239263804</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20656380368098</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1.968</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.529</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.523</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.534</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1.537</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.539</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.402</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.441</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.489</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.447</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.475</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.469</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.495</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.425</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.317</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>1.248</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.252</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.276</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1.298</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>1.332</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1.369</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>1.404</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1.523</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1.671</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>1.717</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1.799</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1.754</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.226</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.216</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1.238</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1.245</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.231</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.187</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.124</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.145</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.181</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.175</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.228</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.225</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.281</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.258</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.112</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.119</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.134</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.153</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1.185</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1.214</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>1.251</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1.348</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>1.493</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1.6</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3924.144</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3380.531</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3369.506</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>3390.363</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3395.361</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3336.095</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3103.155</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2918.134</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2973.117</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3011.863</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2912.496</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2984.164</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2973.36</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3063.689</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2956.109</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2688.184</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2539.975</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2537.07</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2573.434</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2617.923</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>2692.881</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2768.474</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2835.501</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>3064.371</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>3349.839</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>3444.703</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3605.332</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3499.116</t>
+          <t>5138275881.92849</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1951.345</t>
+          <t>4278021980.04339</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1916.662</t>
+          <t>5350199212.91688</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1990.543</t>
+          <t>4931556369.92523</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2018.087</t>
+          <t>5011495896.31602</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2075.033</t>
+          <t>4936822485.74642</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1935.085</t>
+          <t>4769692188.79169</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1768.467</t>
+          <t>4497318414.65623</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1790.512</t>
+          <t>4571241751.77349</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1842.923</t>
+          <t>4654223846.42954</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1877.44</t>
+          <t>4284171498.93259</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2060.236</t>
+          <t>4320918144.91742</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2295.932</t>
+          <t>4053428082.62118</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2646.236</t>
+          <t>4467238696.23129</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2264.985</t>
+          <t>3808242564.34972</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2052.444</t>
+          <t>3636667999.67068</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2005.067</t>
+          <t>3526352080.45967</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2007.635</t>
+          <t>3775652857.26053</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2015.492</t>
+          <t>3559963565.6508</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2333.276</t>
+          <t>3384853749.11332</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2402.843</t>
+          <t>3515603954.83678</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2463.579</t>
+          <t>3639830054.59249</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2534.949</t>
+          <t>3791515900.02053</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2722.3</t>
+          <t>4180467814.10031</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3000.496</t>
+          <t>4489179373.04388</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3074.567</t>
+          <t>4714368580.52689</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>3211.551</t>
+          <t>4346208312.73244</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1395999344.96201</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>872793488.105329</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1388810617.46191</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1249422324.04084</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1337415104.64125</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1464079619.54328</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1194335577.65143</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1361492786.51447</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1129442017.31342</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1238742774.56714</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1221730712.22216</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1263096074.22395</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1111356945.22311</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1300616436.28522</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1151493696.56728</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1042552793.65929</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1134036730.56365</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1143211985.94751</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>995920457.062872</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1092552502.82806</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1098803129.75399</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1151525070.39055</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1198673693.95455</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1573659178.86076</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1416704764.28567</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1536426430.54431</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1172510583.13444</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>64716526.7690168</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>61716312.7527356</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>48861660.0462626</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>42432235.5664176</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1935516899.20123</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>31462197.1914065</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>34509138.5865423</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30745555.5847618</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>58037822.203237</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>24654964.8157788</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>18627054.8678127</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16655432.022629</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>13673353.4403285</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>41448414.0696058</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>9266236127.23582</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>11590304.2602387</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>12687492.1034987</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>394326016.125231</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>86441371.1933298</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>7464586.72501518</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>7200145.62356846</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7003220.94858092</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>6241895.52695373</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>129706692.444772</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>7119353.0242439</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>7049640.26484363</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>6829764.08793309</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8622.5614534511</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>18963.6440621816</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20793.7238027063</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>20831.3849758788</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>21818.9440765941</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>25146.3991406932</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>23575.6214492794</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>21421.147200857</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>19845.5041697561</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>19691.3368700133</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>19642.7968615127</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>21443.679101754</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>21790.1106509783</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>22397.8491933754</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>20785.1476619886</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>21237.4444817836</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>20757.2652580364</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>22968.843691247</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>22918.8128578762</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>23460.8018376122</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>27745.2459734001</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>25547.8036979477</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>27372.4481215017</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>29085.6405573095</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>33158.7752594279</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>32673.586532076</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>32821.6214532973</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19153.4507504199</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>32508.9988818879</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>44281.5873112619</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>41962.3222928432</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>44979.6532914474</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>52966.2475816172</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>51382.7085957056</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>46963.8623719323</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>43850.923542749</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>43630.6574344526</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>43054.9458160622</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>46451.2091164412</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>45146.7258877728</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>49995.1444357428</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>42710.0081763276</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>47034.3354800476</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>47479.900293164</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>56111.2952512185</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>51679.9172091486</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>50861.6208657478</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>59674.3788115101</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>56313.4041845779</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>62018.1692735127</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>66504.7828291234</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>76091.0100854452</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>76016.6335498025</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>68803.3467885474</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.50653132324956</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.23574651574939</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.380074414682406</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.593170669115453</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.508945871028073</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.417295188254956</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.620218836489374</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.298917642102896</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.585306702382459</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.487736629296665</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.536705250361087</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.631099994720988</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.06588182781419</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.03460138298607</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.966997306847734</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.96867152673986</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.768079415737277</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.756135366561729</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.02374796672467</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.135618743676</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.18678248350974</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.13940577613962</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.11479527279509</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.729917206386575</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.11794054624874</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.00111573615306</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.73903763108696</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>795.680140466072</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>711.787219136521</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1141.73842277366</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1008.90045545954</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1074.22899971177</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1189.43831305797</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1006.09517113259</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1211.40029051899</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>986.239973204164</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1049.15962951402</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1039.50541327509</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1028.74741344209</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>907.452392605017</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1015.47192089701</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>915.045849147717</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>898.907392360041</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1019.9089221727</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1021.63716349155</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>877.927060175504</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>947.485929669301</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>927.521099430189</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>948.877256820362</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>958.454457946705</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1167.07309820559</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>949.164059111558</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1004.46235177387</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>732.594438509154</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>849410224.460009</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-482930672.52153</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>483794374.019033</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>294875300.460855</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>471214523.154396</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>887183229.812262</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>631574550.775367</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>705411169.799305</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>557294791.375059</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>847998566.324963</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>467587712.757786</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>384334382.053443</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>104232970.152019</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>339383266.419698</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>515258617.520895</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>750976072.728167</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>767287629.201138</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>952000550.527196</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>850571480.701676</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>913861678.620635</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>742155557.516081</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>847724121.664048</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>978888179.251447</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1226333340.2285</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1300379174.62231</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1472562906.51032</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>706805680.610047</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>947396427.03976</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-447659145.429655</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>494723747.896701</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>306393885.912168</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>484123732.118412</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>862740655.821003</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>589169073.850819</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>663068966.597967</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>538647652.619282</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>844445416.979561</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>468394285.851603</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>385422406.498346</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>141340269.983707</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>418695215.008527</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>503872849.945626</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>705587853.959701</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>717007249.41051</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>895581233.336721</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>754991063.874511</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>818289581.921217</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>666760582.64567</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>733448268.771002</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>910093711.312175</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>1036295713.4364</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1167160368.64528</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>1308750276.0784</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1480496269.54545</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-97986202.5797515</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-35271527.0918752</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-10929373.8776672</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-11518585.4513122</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12909208.9640158</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>24442573.9912586</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>42405476.9245484</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>42342203.2013379</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>18647138.7557773</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>3553149.34540147</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-806573.093816477</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-1088024.44490323</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-37107299.8316884</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-79311948.5888297</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>11385767.5752687</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>45388218.7684658</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>50280379.7906274</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>56419317.1904753</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>95580416.8271658</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>95572096.6994182</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>75394974.8704107</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>114275852.893047</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>68794467.9392718</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>190037626.792106</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>133218805.977031</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>163812630.431913</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-773690588.935405</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1994.39719536582</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1591.37579513942</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1575.68398552978</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1607.35061369536</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1620.9534136537</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1685.78519782316</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1630.09434757002</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1573.50920900369</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1563.49283967806</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1560.87321080733</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1597.4134263586</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1677.98990063463</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1874.68940748921</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>2066.08057464058</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1799.89272091576</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1769.65338851519</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1803.27997122034</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1794.13315460132</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>1776.70310296274</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>2023.46871077103</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>2028.28689331963</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>2030.033484089</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>2026.93495685508</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>2018.93983369673</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>2010.27304583441</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>2010.04541850801</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>2006.60373540159</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1994.12960335691</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2210.9424460432</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2211.83274254842</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2210.00130369625</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2209.37077043184</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2167.70305393125</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2111.27704449578</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2080.81431831111</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2063.66141458949</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2022.19887202935</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2012.7823082241</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2022.88774403432</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2024.07079645981</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2049.70161236343</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2073.73482988465</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2040.67714264007</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2035.88890670072</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2026.89941679248</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2016.95587428562</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2017.61118899762</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>2021.62668676431</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2022.55096404971</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>2019.79983453356</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>2011.89107957843</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>2005.23380106023</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>2006.20930065013</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2004.01163508785</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1483.85230107818</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2540.34547333808</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3310.39989422927</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3152.5540485261</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2568.93890935035</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>4101.39349355421</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5428.79470102641</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6233.08375726164</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>5854.51051417712</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6762.72413953352</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>9555.36147934688</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>10918.1259760505</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>9920.43192681405</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>14006.7468779341</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>12050.8480742491</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>16057.1648363948</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>19961.3209399652</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>24058.9296092859</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>24834.2478404696</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>23164.2638243727</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>23840.3888655674</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>24446.686435949</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>29569.230106613</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>32392.8609154968</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>37052.0262210394</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>38910.9945204177</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>34511.1022063028</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>687767056.036464</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>698591885.220891</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1111912499.63102</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>900805246.08844</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>792334056.429391</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>940349729.611185</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1063917496.8169</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1040141272.06486</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>957280643.595397</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>966255442.186978</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1003354348.50413</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1009942174.49083</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>796506739.124017</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1044390036.05341</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>953394713.727849</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1063162340.76162</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1068789810.19009</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1308918238.45769</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1356422226.22032</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1148930199.69312</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>1181662500.10746</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1225271036.75355</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1413218119.82772</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>1601624389.71713</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1838978912.57826</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2032994131.32547</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1573100006.46946</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2196.15474495681</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3343.13462455837</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4486.59081133443</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4647.90395230744</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3913.45077064983</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5111.8217663613</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6406.72626180886</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>7353.82339616644</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7112.59095751347</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>8442.61803198492</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>11538.7529181759</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>14143.5617251413</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>14884.7539225331</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>18944.9394272279</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>12667.9688783948</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>16790.9939776887</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>21060.9723618417</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>23792.2026922906</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>24169.8323423178</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>22294.228196447</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>24327.2325707356</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>24080.2235184946</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>28288.0263569423</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>31291.318880297</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>33727.1529182437</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>35855.1031450691</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>31782.1997899685</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3924.144</t>
+          <t>1940715305.55501</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3380.531</t>
+          <t>378738234.489632</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3369.506</t>
+          <t>1815875366.39861</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3390.363</t>
+          <t>1477401957.02117</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3395.361</t>
+          <t>1510191069.412</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3336.095</t>
+          <t>1984291386.07923</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3103.155</t>
+          <t>1853211860.59435</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2918.134</t>
+          <t>1933089785.1062</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2973.117</t>
+          <t>1728295193.11959</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3011.863</t>
+          <t>2122329483.43687</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2912.496</t>
+          <t>1802665438.33485</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2984.164</t>
+          <t>1874194623.58306</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2973.36</t>
+          <t>1517221149.02411</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3063.689</t>
+          <t>2060499996.87311</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2956.109</t>
+          <t>1559488212.54162</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2688.184</t>
+          <t>1904621026.29321</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2539.975</t>
+          <t>1962884573.67931</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2537.07</t>
+          <t>2231837224.7387</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2573.434</t>
+          <t>2130882548.4103</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2617.923</t>
+          <t>1970301790.33703</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2692.881</t>
+          <t>1970878747.61873</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2768.474</t>
+          <t>2034129372.38069</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2835.501</t>
+          <t>2268697221.6026</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3064.371</t>
+          <t>2718475790.74985</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>3349.839</t>
+          <t>2835905525.25133</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>3444.703</t>
+          <t>3209009285.35464</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3605.332</t>
+          <t>2014014878.24361</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3499.116</t>
+          <t>-712.302443878634</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1951.345</t>
+          <t>-802.789151220291</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1916.662</t>
+          <t>-1176.19091710516</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1990.543</t>
+          <t>-1495.34990378134</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2018.087</t>
+          <t>-1344.51186129948</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2075.033</t>
+          <t>-1010.42827280709</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1935.085</t>
+          <t>-977.931560782454</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1768.467</t>
+          <t>-1120.7396389048</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1790.512</t>
+          <t>-1258.08044333636</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1842.923</t>
+          <t>-1679.8938924514</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1877.44</t>
+          <t>-1983.39143882907</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2060.236</t>
+          <t>-3225.43574909078</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2295.932</t>
+          <t>-4964.321995719</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2646.236</t>
+          <t>-4938.19254929374</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2264.985</t>
+          <t>-617.120804145617</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2052.444</t>
+          <t>-733.829141293895</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2005.067</t>
+          <t>-1099.65142187647</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2007.635</t>
+          <t>266.726916995305</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2015.492</t>
+          <t>664.415498151853</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2333.276</t>
+          <t>870.035627925749</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2402.843</t>
+          <t>-486.843705168183</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2463.579</t>
+          <t>366.46291745439</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2534.949</t>
+          <t>1281.20374967072</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>2722.3</t>
+          <t>1101.54203519984</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>3000.496</t>
+          <t>3324.87330279568</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>3074.567</t>
+          <t>3055.89137534856</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3211.551</t>
+          <t>2728.90241633431</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4179.704</t>
+          <t>-1252948249.51855</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3657.313</t>
+          <t>319853650.731259</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4352.521</t>
+          <t>-703962866.767593</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4082.648</t>
+          <t>-576596710.932731</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4133.358</t>
+          <t>-717857012.982606</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4052.226</t>
+          <t>-1043941656.46804</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3888.63</t>
+          <t>-789294363.777444</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3691.741</t>
+          <t>-892948513.041342</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3753.632</t>
+          <t>-771014549.524189</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3814.839</t>
+          <t>-1156074041.24989</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3528.47</t>
+          <t>-799311089.830724</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3579.202</t>
+          <t>-864252449.092225</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3381.142</t>
+          <t>-720714409.900093</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3694.491</t>
+          <t>-1016109960.8197</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3196.751</t>
+          <t>-606093498.813769</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>3014.043</t>
+          <t>-841458685.531595</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2916.322</t>
+          <t>-894094763.489217</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3093.059</t>
+          <t>-922918986.28101</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2971.015</t>
+          <t>-774460322.189976</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2815.792</t>
+          <t>-821371590.64391</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2927.919</t>
+          <t>-789216247.511267</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>3023.36</t>
+          <t>-808858335.627142</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>3146.34</t>
+          <t>-855479101.774877</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3451.675</t>
+          <t>-1116851401.03272</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>3707.704</t>
+          <t>-996926612.673073</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3892.33</t>
+          <t>-1176015154.02916</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>3643.763</t>
+          <t>-440914871.774151</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2094.82848267771</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2619.93816054538</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>3545.49744856156</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>3866.1019467767</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>4135.25497149857</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>4865.71447063075</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>4788.67559352596</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>5633.0901042171</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>6151.98377057033</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>6402.67233856946</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>7497.60436747458</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>9120.08668925499</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>11259.7412278092</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>11178.983524382</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>10023.0270825782</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>9306.43211803678</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>11258.0749224645</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>11474.4242543157</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>11831.5396785077</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>12487.9639814096</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>12601.7300979688</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>13036.7371033159</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>14189.0362673879</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>15664.7758508658</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>16228.6902948718</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>16688.0024556228</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>17364.4403308597</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2313.165</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2495.521</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2512.344</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2448.176</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2431</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2343.819</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2188.449</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2051.316</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2068.796</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2100.539</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1954.552</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1994.703</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1956.391</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2001.325</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1853.31</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1642.067</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>1541.651</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1545.542</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1578.759</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1561.322</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>1634.559</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1651.288</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>1673.43</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>1828.313</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1956.285</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>2026.337</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2073.295</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2954.74495311511</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>3648.25318937686</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5047.57594504258</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5716.07666096145</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>6325.07478764131</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>7028.56412974337</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>7255.89153829477</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>8866.7419676004</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>9306.45527524237</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>10495.8142679364</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>12453.4280823006</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>14733.6205942332</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>17800.423827152</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19540.9257699191</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>16373.0091049903</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>15228.5294430017</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17248.7459313975</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>18538.8847719732</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>18648.0767892857</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19690.024808896</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>21211.4642830676</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22073.8981565666</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>24321.7572310901</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27095.8085933414</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27741.8218157938</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>28046.6596903281</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>29770.8904232942</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1112.542</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>767.044</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1165.963</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1072.971</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1138.476</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>1229.17</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1005.072</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>1164.353</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>969.461</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1072.732</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1050.52</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1083.028</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>966.45</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1111.193</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1009.857</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>896.972</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>979.985</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>981.37</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>864.382</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>956.056</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>955.692</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1001.166</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>1040.982</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>1357.562</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>1223.502</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>1321.49</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1020.772</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>214.52</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>154.4</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>64.38</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>85.52</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>77.26</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>68.82</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>92.53</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>51.88</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>84.69</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>71.8</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>78.72</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>90.23</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>137.56</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>138.14</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>124.29</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>128.82</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>104.6</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>104.57</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>133.17</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>144.05</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>151.42</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>146.07</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>143.52</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>100.53</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>145.24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>132.66</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>214.62</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>65.558</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>69.837</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>52.476</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>46.734</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2206.828</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>33.393</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>37.664</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>67.604</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>26.413</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>20.269</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>18.068</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>15.105</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>46.5</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>10481.316</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>12.615</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>13.941</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>489.172</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>97.421</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>8.053</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>7.745</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>6.727</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>146.316</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>7.665</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>7.555</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>7.356</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3063.55975691945</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4159.03908536548</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>5633.4536299236</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6285.16414259549</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>6074.33317263012</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>7985.5406434054</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>9265.51056780249</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>9307.28384908377</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>10579.6586119109</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>11499.1104140667</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>12914.1298456587</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>14293.8427925227</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>17180.0988102615</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>19911.0557236608</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>16051.2977601278</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>18772.6267537527</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>20577.2807050137</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>22004.3762636577</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>23821.0411415375</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>24600.4501078696</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>23984.733685486</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>25052.5949406338</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>26853.0325376552</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>28230.1948501998</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>31464.6892383006</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>32856.5501213759</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>32670.530412638</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3499116085.38316</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1951345000.00024</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1916661999.99846</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1990542999.99992</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2018086999.99899</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2075033000.00084</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1935085000.00027</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1768466999.99948</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1790511999.99933</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1842923000.00012</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1877439999.99919</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2060235999.99879</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2295932117.35151</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2646236000.00031</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2264984999.99999</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2052444000.00013</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2005066999.99958</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2007634999.9997</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2015492000.00049</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2333275603.48973</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2402843436.97171</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2463579386.96312</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2534949461.59891</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>2722300090.4994</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>3000496462.34438</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>3074567107.60368</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>3211550610.05296</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3924143786.28414</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3380531000.00017</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3369505999.99852</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3390362999.99981</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3395360999.99956</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3336095000.00038</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3103154999.99957</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2918133999.99955</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2973116999.99912</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3011863000.00026</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2912495999.99974</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2984163999.99912</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2973359999.99886</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3063689000.00028</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2956109000.00011</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2688184000.00018</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2539974999.99962</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2537069999.99991</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2573434000.00055</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2617922784.04929</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>2692880683.99598</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2768473930.61529</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2835500938.56604</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>3064370601.77711</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>3349839050.95009</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>3444703435.36961</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>3605331542.37685</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2313165399.49036</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2495520899.13575</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2512343650.66576</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2448175974.51419</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2431000256.78925</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2343819212.83045</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2188449393.69226</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2051315946.00387</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2068795590.07109</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2100538818.74638</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1954551535.91253</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1994703343.29273</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1956390960.78991</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2001325123.83475</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1853309971.42144</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1642067097.43882</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1541650784.33976</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1545542299.86241</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1578759083.76194</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1561322303.64536</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>1634559058.92381</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>1651288269.19836</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1673430117.18802</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>1828313378.82478</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1956284845.777</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>2026337165.52351</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2073294551.15144</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1967847.91704524</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1529000.00000005</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1523400.00000012</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1534099.99999973</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1536799.99999996</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1539000.00000009</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1469799.99999984</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1402400.00000002</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1440700.00000002</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1489399.99999988</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1446999.99999973</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1475199.99999985</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1468999.9999997</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1494700.00000032</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1425499.99999978</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1317300.0000002</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1247599.9999999</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1251700.00000038</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1275899.99999976</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1297535.81776572</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>1332036.57313509</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>1368803.0511093</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>1403852.44621077</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>1523129.47399678</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1670547.86787402</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>1717020.96797843</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1799057.19071276</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1754473.02749608</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1226200.00000018</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1216400.00000002</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1238399.99999975</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1245000.00000008</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1230900.00000018</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1187099.99999994</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1123900.00000015</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1145200.00000001</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1180699.99999994</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1175299.99999995</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1227799.99999976</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1224699.99999972</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1280800.00000032</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1258399.99999978</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1159800.00000012</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1111899.99999983</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1119000.00000046</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1134399.99999975</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1153106.8363299</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>1184666.45171633</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>1213565.88759357</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>1250631.87302865</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>1348380.98940016</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1492581.55182544</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>1529600.81364024</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1600490.69649031</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3924143786.28414</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3380531000.00017</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3369505999.99852</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3390362999.99981</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3395360999.99956</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3336095000.00038</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3103154999.99957</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2918133999.99955</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2973116999.99912</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3011863000.00026</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2912495999.99974</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2984163999.99912</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2973359999.99886</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3063689000.00028</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2956109000.00011</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2688184000.00018</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2539974999.99962</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2537069999.99991</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2573434000.00055</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2617922784.04929</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>2692880683.99598</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2768473930.61529</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2835500938.56604</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>3064370601.77711</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>3349839050.95009</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>3444703435.36961</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3605331542.37685</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3499116085.38316</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1951345000.00024</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1916661999.99846</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1990542999.99992</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2018086999.99899</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2075033000.00084</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1935085000.00027</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1768466999.99948</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1790511999.99933</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1842923000.00012</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1877439999.99919</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2060235999.99879</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2295932117.35151</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2646236000.00031</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2264984999.99999</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2052444000.00013</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2005066999.99958</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2007634999.9997</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2015492000.00049</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2333275603.48973</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>2402843436.97171</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2463579386.96312</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2534949461.59891</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>2722300090.4994</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>3000496462.34438</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>3074567107.60368</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>3211550610.05296</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>11266.3216425826</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>14227.196952276</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19372.4484295735</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>21545.0945838597</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>21394.0578968097</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>26086.0493649402</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>28846.591918961</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>32766.563999545</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>34505.4231858228</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>37991.8529595516</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>44896.8666306538</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>51687.0940388879</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>60753.0814103217</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>70543.6422327505</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>55940.0870705774</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>59421.1729714737</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>68987.5467725817</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>72961.5155845789</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>74790.7649752724</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>76947.2815753448</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>78445.572373855</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>81612.237567575</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>90343.0603350119</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>97255.8062508425</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>102770.930184601</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>105629.092683039</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>106727.50150344</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3185.62803299093</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3890.01479010425</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5253.84379162834</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>5962.82075160565</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>6528.29988547634</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7296.50197862394</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7462.52858531726</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9170.65672044465</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>9788.58966478783</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>10805.0549013059</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12816.7280499287</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>15174.316622427</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>18398.7953417805</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>20078.8197636842</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>16891.3603161131</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>15648.073316843</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>17798.8216947941</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>19013.4680443279</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>19188.144709095</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>20316.591672051</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>21885.5066591948</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>22739.0317043408</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>25063.6901840341</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>27737.2539987008</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>28523.9062123854</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>28726.6458203556</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>30466.6995932318</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
